--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_r2/post_rank_positive_return/staggered_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_r2/post_rank_positive_return/staggered_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$N$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -488,30 +494,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>基准收益</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>超额收益</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>年化波动</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>跟踪误差</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>信息比率</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>策略最大回撤</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>基准最大回撤</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>超额最大回撤</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Calmar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>年化换手率（单边）</t>
         </is>
@@ -527,21 +563,39 @@
         <v>0.03793078684321749</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>-0.02176047699359285</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.06101906785912936</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0.2841236694280108</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="F2" s="3" t="n">
+        <v>0.2357614089164432</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>0.237104458313754</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.3397265673818745</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="I2" s="4" t="n">
+        <v>0.3858943673485293</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>0.2119021211342235</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="K2" s="3" t="n">
+        <v>0.1506490308477421</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.2070972126380217</v>
+      </c>
+      <c r="M2" s="4" t="n">
         <v>0.2027731654620278</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>16.04436537809722</v>
       </c>
     </row>
@@ -555,21 +609,39 @@
         <v>-0.2428359175325104</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>-0.2255774308756096</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>-0.02228561943438001</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0.2218785776524475</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0.1499575853340444</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>-1.260806514139231</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>-1.614880326710635</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="I3" s="4" t="n">
+        <v>-0.1365200407559806</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0.2659780445013709</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="K3" s="3" t="n">
+        <v>0.2845881262232945</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.1379525679889922</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>-0.9455275593418139</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>15.99641150372136</v>
       </c>
     </row>
@@ -583,21 +655,39 @@
         <v>-0.1511269368642016</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>-0.1141699148043651</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>-0.0417202155102615</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0.2121495641389554</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0.1639059735608032</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>-0.7681929519803301</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>-1.040052409747037</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="I4" s="4" t="n">
+        <v>-0.1890924897055987</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>0.2732580054751854</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="K4" s="3" t="n">
+        <v>0.2177913835362562</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.1206767440456211</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>-0.5740172283320698</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>16.59502330015335</v>
       </c>
     </row>
@@ -611,21 +701,39 @@
         <v>0.02505540692422126</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0.1298071537204202</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-0.09271648391608778</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0.2600726615955116</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0.1341358310170812</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0.1692701917515242</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.2872318736503165</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="I5" s="4" t="n">
+        <v>-0.6995322955028257</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.2718191181209891</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="K5" s="3" t="n">
+        <v>0.1515696200238076</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.2079631421358666</v>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>0.09603501828943056</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>18.1794828466092</v>
       </c>
     </row>
@@ -639,54 +747,90 @@
         <v>0.2813475532408765</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0.2243203183030871</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.04657868866933668</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>0.2564279243053336</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="F6" s="3" t="n">
+        <v>0.1446783950970909</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>1.073493104787577</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>1.528048900900751</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="I6" s="4" t="n">
+        <v>0.4572437365571642</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>0.1572460742095678</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0.1188658802983931</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.1069558365809186</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>1.864383494967752</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>17.90450823132246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026年截至07-31</t>
+          <t>2026年截至07-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1450224449669515</v>
+        <v>0.1416450931892981</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3443800347711813</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.8417863238676052</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1.177912694778191</v>
+        <v>-0.01504143451691176</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.1590793087111855</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.3456264134392768</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>0.2080001984899902</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.8295107610765103</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.160738429762212</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1.456847628597234</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>0.2043601334845871</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>1.361725627810286</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>15.93818830985241</v>
+      <c r="K7" s="3" t="n">
+        <v>0.127969093077366</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.1175941644296936</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1.339154052559206</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>15.94191626720902</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>